--- a/virtual-physics-lab/app/dl/HCI_Q2a_discharge.xlsx
+++ b/virtual-physics-lab/app/dl/HCI_Q2a_discharge.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +102,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -668,55 +671,55 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.303</v>
       </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.192</v>
       </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="C7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.121</v>
       </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.077</v>
       </c>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.047</v>
       </c>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>0.031</v>
       </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -790,10 +793,10 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.303</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>LN(B6)</f>
         <v/>
       </c>
@@ -802,7 +805,7 @@
           <t>gradient</t>
         </is>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>SLOPE(C6:C11,A6:A11)</f>
         <v/>
       </c>
@@ -816,10 +819,10 @@
       <c r="A7" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.192</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <f>LN(B7)</f>
         <v/>
       </c>
@@ -828,7 +831,7 @@
           <t>τ = −1/gradient</t>
         </is>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f>-1/SLOPE(C6:C11,A6:A11)</f>
         <v/>
       </c>
@@ -842,10 +845,10 @@
       <c r="A8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.121</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>LN(B8)</f>
         <v/>
       </c>
@@ -854,7 +857,7 @@
           <t>C = τ/R₂</t>
         </is>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f>-1/SLOPE(C6:C11,A6:A11)/10000</f>
         <v/>
       </c>
@@ -868,10 +871,10 @@
       <c r="A9" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.077</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <f>LN(B9)</f>
         <v/>
       </c>
@@ -880,10 +883,10 @@
       <c r="A10" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.047</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <f>LN(B10)</f>
         <v/>
       </c>
@@ -892,10 +895,10 @@
       <c r="A11" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>0.031</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>LN(B11)</f>
         <v/>
       </c>
